--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104473_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104473_W2.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5438</v>
+        <v>3.2404</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6918</v>
+        <v>5.3455</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.148</v>
+        <v>-2.1051</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.2657</v>
+        <v>-1.281</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2296</v>
+        <v>0.2161</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.4954</v>
+        <v>-1.4971</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3481</v>
+        <v>1.3121</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0177</v>
+        <v>0.9923</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3304</v>
+        <v>0.3198</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.6139</v>
+        <v>-2.5931</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.8258</v>
+        <v>-1.8169</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R2" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2117</v>
+        <v>-0.0721</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2389</v>
+        <v>-0.523</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4506</v>
+        <v>0.4509</v>
       </c>
       <c r="V2" t="n">
-        <v>2.7831</v>
+        <v>2.7725</v>
       </c>
       <c r="W2" t="n">
-        <v>6.1704</v>
+        <v>6.1499</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.3873</v>
+        <v>-3.3774</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5924</v>
+        <v>2.3264</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9417</v>
+        <v>2.4926</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3493</v>
+        <v>-0.1662</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3325</v>
+        <v>1.3266</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8874</v>
+        <v>0.8875</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="J3" t="n">
-        <v>3.005</v>
+        <v>2.9762</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2268</v>
+        <v>2.2096</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7782</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6725</v>
+        <v>-1.6496</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3393</v>
+        <v>-1.3221</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4472</v>
+        <v>-0.7028</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9557</v>
+        <v>-0.3651</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4915</v>
+        <v>-0.3377</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.795</v>
+        <v>0.7252</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.3436</v>
+        <v>1.0282</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1386</v>
+        <v>-0.3031</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.1699</v>
+        <v>-0.6944</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2135</v>
+        <v>-0.3014</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3834</v>
+        <v>-0.393</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7206</v>
+        <v>1.9276</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7029</v>
+        <v>0.6615</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.4234</v>
+        <v>1.2661</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4494</v>
+        <v>-2.6219</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4894</v>
+        <v>-0.9629</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04</v>
+        <v>-1.659</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>2.0487</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5113</v>
+        <v>-0.3624</v>
       </c>
       <c r="T4" t="n">
-        <v>0.738</v>
+        <v>-0.6717</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7733</v>
+        <v>0.3093</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.2667</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6708</v>
+        <v>0.5944</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6951000000000001</v>
+        <v>-0.9111</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0243</v>
+        <v>1.5054</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6984</v>
+        <v>-0.5717</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2986</v>
+        <v>0.5427</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3998</v>
+        <v>-1.1145</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9472</v>
+        <v>1.0172</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6785</v>
+        <v>1.003</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2688</v>
+        <v>0.0142</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6457</v>
+        <v>-1.589</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9771</v>
+        <v>-0.4603</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6685</v>
+        <v>-1.1287</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2683</v>
+        <v>2.7316</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4023</v>
+        <v>-0.0419</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0253</v>
+        <v>-0.5625</v>
       </c>
       <c r="U5" t="n">
-        <v>0.623</v>
+        <v>0.5206</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.27</v>
+        <v>-0.1578</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.27</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.506</v>
+        <v>0.2331</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7134</v>
+        <v>-0.1328</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2194</v>
+        <v>0.3658</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5678</v>
+        <v>-0.175</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5411</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1089</v>
+        <v>0.6985</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0438</v>
+        <v>0.0115</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0146</v>
+        <v>-0.4277</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0292</v>
+        <v>0.4392</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6116</v>
+        <v>-0.1865</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4735</v>
+        <v>-0.4458</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1381</v>
+        <v>0.2593</v>
       </c>
       <c r="P6" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>2.722</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1264</v>
+        <v>0.2195</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3962</v>
+        <v>0.0834</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2698</v>
+        <v>0.1361</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1607</v>
+        <v>-0.2667</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. KUSTURICA</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5195</v>
+        <v>0.181</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-1.7646</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5195</v>
+        <v>1.9456</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7463</v>
+        <v>-1.1674</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.218</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7463</v>
+        <v>-1.3854</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0.7376</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.6927</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.4303</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7463</v>
+        <v>-0.4298</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.4747</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7463</v>
+        <v>0.0449</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.8931</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.3388</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.5543</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>N. KUSTURICA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5663</v>
+        <v>-0.5171</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0391</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6054</v>
+        <v>-0.5171</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9331</v>
+        <v>-0.7447</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.2424</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3092</v>
+        <v>-0.7447</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.1605</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.2725</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.112</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2274</v>
+        <v>-0.7447</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0301</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1973</v>
+        <v>-0.7447</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5275</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2411</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2864</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6413</v>
+        <v>-1.3604</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8305</v>
+        <v>-1.8396</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1892</v>
+        <v>0.4792</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1793</v>
+        <v>-2.6147</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8803</v>
+        <v>-2.3028</v>
       </c>
       <c r="I9" t="n">
-        <v>0.701</v>
+        <v>-0.3119</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0224</v>
+        <v>-1.1981</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4227</v>
+        <v>-2.1728</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4451</v>
+        <v>0.9747</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2017</v>
+        <v>-1.4166</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4576</v>
+        <v>-0.13</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2559</v>
+        <v>-1.2866</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>2.5039</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>2.7316</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.0512</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6261</v>
+        <v>-0.4138</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0197</v>
+        <v>0.3627</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.27</v>
+        <v>-1.1984</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.27</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1399</v>
+        <v>-1.9909</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.334</v>
+        <v>-1.5071</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1941</v>
+        <v>-0.4838</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5899</v>
+        <v>-1.9258</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.2912</v>
+        <v>-2.2403</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2986</v>
+        <v>0.3145</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1514</v>
+        <v>-2.171</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.1482</v>
+        <v>-2.2827</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9967</v>
+        <v>0.1117</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4384</v>
+        <v>0.2452</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1431</v>
+        <v>0.0424</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2954</v>
+        <v>0.2028</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4952</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>2.722</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8431999999999999</v>
+        <v>1.0927</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9557</v>
+        <v>0.7126</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1125</v>
+        <v>0.3801</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2019</v>
+        <v>-0.7025</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2019</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6007</v>
+        <v>-2.0018</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2857</v>
+        <v>-2.4921</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.4903</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1837</v>
+        <v>-0.1813</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3708</v>
+        <v>0.376</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5545</v>
+        <v>-0.5572</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4975</v>
+        <v>0.4774</v>
       </c>
       <c r="K11" t="n">
-        <v>0.876</v>
+        <v>0.8651</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6812</v>
+        <v>-0.6587</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4455</v>
+        <v>0.1615</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9043</v>
+        <v>-0.077</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4588</v>
+        <v>0.2385</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9351</v>
+        <v>-3.9643</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.03</v>
+        <v>-3.9758</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0949</v>
+        <v>0.0115</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.558</v>
+        <v>-1.5613</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7503</v>
+        <v>-0.7524</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8077</v>
+        <v>-0.8089</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4834</v>
+        <v>-1.4903</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0745</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1503</v>
+        <v>-0.1754</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2782</v>
+        <v>-0.2091</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1279</v>
+        <v>0.0338</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.087</v>
+        <v>-4.5092</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8622</v>
+        <v>-3.2535</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2248</v>
+        <v>-1.2557</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.8219</v>
+        <v>-1.8191</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.58</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.2448</v>
+        <v>-1.2391</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8797</v>
+        <v>0.8622</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7304</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.7016</v>
+        <v>-2.6813</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3075</v>
+        <v>-1.2932</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4301</v>
+        <v>0.0139</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1785</v>
+        <v>-0.1745</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2516</v>
+        <v>0.1884</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8804999999999999</v>
+        <v>-0.8829</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8163</v>
+        <v>-0.8114</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.381799999999998</v>
+        <v>-7.0432</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.031700000000001</v>
+        <v>-7.0103</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3501000000000005</v>
+        <v>-0.03320000000000012</v>
       </c>
       <c r="G14" t="n">
-        <v>-11.3815</v>
+        <v>-11.4098</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.797499999999999</v>
+        <v>-4.8101</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.584099999999999</v>
+        <v>-6.599600000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2278</v>
+        <v>2.9872</v>
       </c>
       <c r="K14" t="n">
-        <v>1.669099999999999</v>
+        <v>1.5163</v>
       </c>
       <c r="L14" t="n">
-        <v>1.5587</v>
+        <v>1.4708</v>
       </c>
       <c r="M14" t="n">
-        <v>-14.6094</v>
+        <v>-14.397</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.466600000000001</v>
+        <v>-6.3262</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.1425</v>
+        <v>-8.070500000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>4.536700000000001</v>
+        <v>4.5526</v>
       </c>
       <c r="Q14" t="n">
-        <v>-15.8782</v>
+        <v>-15.9341</v>
       </c>
       <c r="R14" t="n">
-        <v>20.415</v>
+        <v>20.487</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6199999999999997</v>
+        <v>0.9749000000000003</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.2228</v>
+        <v>-1.8619</v>
       </c>
       <c r="U14" t="n">
-        <v>2.8427</v>
+        <v>2.837</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.1569</v>
+        <v>-1.161</v>
       </c>
       <c r="W14" t="n">
-        <v>7.841800000000001</v>
+        <v>7.798999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.998600000000001</v>
+        <v>-8.959900000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7615</v>
+        <v>3.4517</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9598</v>
+        <v>1.6811</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8017</v>
+        <v>1.7706</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1926</v>
+        <v>1.1853</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4573</v>
+        <v>-0.4621</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6499</v>
+        <v>1.6474</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1142</v>
+        <v>1.0819</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.0847</v>
+        <v>-1.1074</v>
       </c>
       <c r="L15" t="n">
-        <v>2.199</v>
+        <v>2.1893</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0784</v>
+        <v>0.1033</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6274</v>
+        <v>0.6452</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.2914</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0212</v>
+        <v>-0.214</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.013</v>
+        <v>-0.0774</v>
       </c>
       <c r="V15" t="n">
-        <v>3.0144</v>
+        <v>3.013</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
-        <v>0.829</v>
+        <v>0.8341</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GOLOMAN</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2971</v>
+        <v>3.2552</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4572</v>
+        <v>1.9693</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8399</v>
+        <v>1.2859</v>
       </c>
       <c r="G16" t="n">
-        <v>2.0013</v>
+        <v>1.2076</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0044</v>
+        <v>-0.382</v>
       </c>
       <c r="I16" t="n">
-        <v>0.997</v>
+        <v>1.5896</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5421</v>
+        <v>1.2493</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4302</v>
+        <v>0.0205</v>
       </c>
       <c r="L16" t="n">
-        <v>0.112</v>
+        <v>1.2288</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4592</v>
+        <v>-0.0417</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4258</v>
+        <v>-0.4025</v>
       </c>
       <c r="O16" t="n">
-        <v>0.885</v>
+        <v>0.3608</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.0476</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0907</v>
+        <v>-0.3695</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4228</v>
+        <v>0.4171</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0091</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1853</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>G. GOLOMAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0394</v>
+        <v>3.2439</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8647</v>
+        <v>2.3157</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1747</v>
+        <v>0.9282</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2036</v>
+        <v>2.0025</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3824</v>
+        <v>0.9997</v>
       </c>
       <c r="I17" t="n">
-        <v>1.586</v>
+        <v>1.0028</v>
       </c>
       <c r="J17" t="n">
-        <v>1.259</v>
+        <v>1.5284</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0275</v>
+        <v>1.4167</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2315</v>
+        <v>0.1117</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0554</v>
+        <v>0.4741</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4099</v>
+        <v>-0.4169</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3546</v>
+        <v>0.8911</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1642</v>
+        <v>0.4599</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4869</v>
+        <v>-0.0258</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3227</v>
+        <v>0.4857</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0927</v>
+        <v>1.0091</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>2.1789</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.1698</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. JIMENEZ</t>
+          <t>K. ZORIKS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.6985</v>
+        <v>2.5785</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6407</v>
+        <v>0.5977</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0579</v>
+        <v>1.9808</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4007</v>
+        <v>2.7241</v>
       </c>
       <c r="H18" t="n">
-        <v>0.199</v>
+        <v>0.3242</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2017</v>
+        <v>2.3998</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8429</v>
+        <v>3.5827</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3188</v>
+        <v>1.4307</v>
       </c>
       <c r="L18" t="n">
-        <v>2.1617</v>
+        <v>2.1521</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5578</v>
+        <v>-0.8587</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5178</v>
+        <v>-1.1064</v>
       </c>
       <c r="O18" t="n">
-        <v>0.04</v>
+        <v>0.2477</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.4537</v>
+        <v>-3.6421</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>2.2763</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.0534</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0907</v>
+        <v>-0.4324</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4824</v>
+        <v>0.4857</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1826</v>
+        <v>1.1669</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3433</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.489</v>
+        <v>2.4051</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8492</v>
+        <v>0.8259</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6398</v>
+        <v>1.5792</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6348</v>
+        <v>1.6405</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8209</v>
+        <v>2.8231</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1861</v>
+        <v>-1.1826</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3992</v>
+        <v>1.3793</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0363</v>
+        <v>2.02</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2356</v>
+        <v>0.2613</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7847</v>
+        <v>0.8032</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0293</v>
+        <v>-0.1242</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2571</v>
+        <v>-0.2559</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2277</v>
+        <v>0.1317</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2507</v>
+        <v>-0.2494</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4114</v>
+        <v>-0.4072</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. ZORIKS</t>
+          <t>M. JIMENEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6695</v>
+        <v>2.1177</v>
       </c>
       <c r="E20" t="n">
-        <v>0.158</v>
+        <v>1.5045</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5115</v>
+        <v>0.6133</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7178</v>
+        <v>2.4034</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3188</v>
+        <v>0.2064</v>
       </c>
       <c r="I20" t="n">
-        <v>2.399</v>
+        <v>2.197</v>
       </c>
       <c r="J20" t="n">
-        <v>3.599</v>
+        <v>1.8278</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4373</v>
+        <v>-0.3242</v>
       </c>
       <c r="L20" t="n">
-        <v>2.1617</v>
+        <v>2.1521</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8812</v>
+        <v>0.5755</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1185</v>
+        <v>0.5306</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2373</v>
+        <v>0.0449</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.6293</v>
+        <v>-0.4553</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2683</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8571</v>
+        <v>-0.015</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9043</v>
+        <v>-0.0258</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0472</v>
+        <v>0.0108</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1698</v>
+        <v>-1.1812</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0771</v>
+        <v>-1.3389</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9864000000000001</v>
+        <v>1.5057</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5581</v>
+        <v>-1.1016</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5445</v>
+        <v>2.6073</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1218</v>
+        <v>-0.1107</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8077</v>
+        <v>0.8089</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3574</v>
+        <v>-0.372</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6132</v>
+        <v>-0.6173</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2558</v>
+        <v>0.2453</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2356</v>
+        <v>0.2613</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7836</v>
+        <v>-0.2821</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9739</v>
+        <v>-0.5021</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1902</v>
+        <v>0.22</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4609</v>
+        <v>0.0997</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5795</v>
+        <v>1.2792</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1186</v>
+        <v>-1.1795</v>
       </c>
       <c r="G22" t="n">
-        <v>3.9155</v>
+        <v>3.8914</v>
       </c>
       <c r="H22" t="n">
-        <v>2.2469</v>
+        <v>2.2324</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6685</v>
+        <v>1.659</v>
       </c>
       <c r="J22" t="n">
-        <v>4.7966</v>
+        <v>4.7501</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2645</v>
+        <v>2.2333</v>
       </c>
       <c r="L22" t="n">
-        <v>2.5321</v>
+        <v>2.5168</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8812</v>
+        <v>-0.8587</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0176</v>
+        <v>-0.0009</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6859</v>
+        <v>0.3578</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0907</v>
+        <v>-0.1443</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5952</v>
+        <v>0.5021</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6454</v>
+        <v>-1.6455</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.9668</v>
+        <v>-1.9611</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9007</v>
+        <v>-1.3932</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1255</v>
+        <v>0.357</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0262</v>
+        <v>-1.7502</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2101</v>
+        <v>-0.1941</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2292</v>
+        <v>1.2401</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.4393</v>
+        <v>-1.4343</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8393</v>
+        <v>0.8357</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7239</v>
       </c>
       <c r="L23" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0494</v>
+        <v>-1.0298</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5019</v>
+        <v>0.5162</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.5513</v>
+        <v>-1.546</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1774</v>
+        <v>-0.6933</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4869</v>
+        <v>-0.251</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6905</v>
+        <v>-0.4422</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.4205</v>
+        <v>-1.4163</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4205</v>
+        <v>-1.4163</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1898</v>
+        <v>-3.0617</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.134</v>
+        <v>-1.5246</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0558</v>
+        <v>-1.5371</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.4924</v>
+        <v>-2.4929</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.3837</v>
+        <v>-1.3925</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1088</v>
+        <v>-1.1005</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9745</v>
+        <v>-1.0041</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3748</v>
+        <v>-0.4007</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5998</v>
+        <v>-0.6035</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5179</v>
+        <v>-1.4888</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0089</v>
+        <v>-0.9918</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0363</v>
+        <v>0.1533</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1179</v>
+        <v>-0.4718</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1542</v>
+        <v>0.6251</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.5068</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="25">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.93</v>
+        <v>-6.0212</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.5924</v>
+        <v>-7.8712</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6624</v>
+        <v>1.85</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8604000000000001</v>
+        <v>-0.8472</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1312</v>
+        <v>0.1402</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9915</v>
+        <v>-0.9874000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.451</v>
+        <v>-0.4623</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9351</v>
+        <v>0.9308</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3861</v>
+        <v>-1.3931</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4094</v>
+        <v>-0.3849</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P25" t="n">
-        <v>-6.3513</v>
+        <v>-6.3737</v>
       </c>
       <c r="Q25" t="n">
-        <v>-7.9391</v>
+        <v>-7.9671</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5746</v>
+        <v>0.4972</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0907</v>
+        <v>-0.1443</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4839</v>
+        <v>0.6415</v>
       </c>
       <c r="V25" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W25" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>7.3818</v>
+        <v>8.181399999999998</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3500999999999994</v>
+        <v>0.03299999999999947</v>
       </c>
       <c r="F26" t="n">
-        <v>7.0318</v>
+        <v>8.1485</v>
       </c>
       <c r="G26" t="n">
-        <v>11.3816</v>
+        <v>11.4099</v>
       </c>
       <c r="H26" t="n">
-        <v>4.7976</v>
+        <v>4.8099</v>
       </c>
       <c r="I26" t="n">
-        <v>6.584099999999999</v>
+        <v>6.599699999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>14.6094</v>
+        <v>14.3968</v>
       </c>
       <c r="K26" t="n">
-        <v>6.466699999999999</v>
+        <v>6.326300000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>8.142799999999999</v>
+        <v>8.070499999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.2279</v>
+        <v>-2.9871</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.669</v>
+        <v>-1.5162</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.5585</v>
+        <v>-1.4708</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="Q26" t="n">
-        <v>-20.4149</v>
+        <v>-20.4869</v>
       </c>
       <c r="R26" t="n">
-        <v>15.8783</v>
+        <v>15.9343</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6198999999999999</v>
+        <v>0.1631999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.843</v>
+        <v>-2.8369</v>
       </c>
       <c r="U26" t="n">
-        <v>2.222799999999999</v>
+        <v>3.0001</v>
       </c>
       <c r="V26" t="n">
-        <v>1.1569</v>
+        <v>1.161</v>
       </c>
       <c r="W26" t="n">
-        <v>8.998600000000001</v>
+        <v>8.959899999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.841900000000001</v>
+        <v>-7.7989</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104473_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104473_W2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-3.3774</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.8114</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-8.959900000000001</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.8341</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.1698</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.4072</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.3389</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.9611</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.4163</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104473_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-7.7989</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
